--- a/Nuevos DeepWins/Problem6_HierarchicalXOR/Res/Comparativa_25_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem6_HierarchicalXOR/Res/Comparativa_25_Neuronas.xlsx
@@ -581,7 +581,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.24997</v>
+        <v>0.249975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
         <v>0.671096</v>
       </c>
       <c r="J2" t="n">
-        <v>0.250173</v>
+        <v>0.250181</v>
       </c>
       <c r="K2" t="n">
         <v>0.485</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_3.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_4.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.106383</v>
+        <v>0.201774</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -699,25 +699,25 @@
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.856258</v>
+        <v>0.689424</v>
       </c>
       <c r="H3" t="n">
-        <v>0.855198</v>
+        <v>0.6373760000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.855728</v>
+        <v>0.6623790000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.116003</v>
+        <v>0.196019</v>
       </c>
       <c r="K3" t="n">
-        <v>0.831633</v>
+        <v>0.687831</v>
       </c>
       <c r="L3" t="n">
-        <v>0.840206</v>
+        <v>0.670103</v>
       </c>
       <c r="M3" t="n">
-        <v>0.835897</v>
+        <v>0.678851</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_14.txt</t>
+          <t>_4_25_1_1790733931_10.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -783,42 +783,42 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.249977</v>
+        <v>0.082273</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E4" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.505</v>
+        <v>0.900125</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.892327</v>
       </c>
       <c r="I4" t="n">
-        <v>0.671096</v>
+        <v>0.896209</v>
       </c>
       <c r="J4" t="n">
-        <v>0.250179</v>
+        <v>0.089388</v>
       </c>
       <c r="K4" t="n">
-        <v>0.485</v>
+        <v>0.876289</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.876289</v>
       </c>
       <c r="M4" t="n">
-        <v>0.653199</v>
+        <v>0.876289</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,28 +854,28 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_16.txt</t>
+          <t>_4_25_1_1790733931_8.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z4" t="n">
         <v>25</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.201774</v>
+        <v>0.106383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.689424</v>
+        <v>0.856258</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6373760000000001</v>
+        <v>0.855198</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6623790000000001</v>
+        <v>0.855728</v>
       </c>
       <c r="J5" t="n">
-        <v>0.196019</v>
+        <v>0.116003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.687831</v>
+        <v>0.831633</v>
       </c>
       <c r="L5" t="n">
-        <v>0.670103</v>
+        <v>0.840206</v>
       </c>
       <c r="M5" t="n">
-        <v>0.678851</v>
+        <v>0.835897</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_10.txt</t>
+          <t>_4_25_1_1790733931_14.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -985,42 +985,42 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.249974</v>
+        <v>0.128928</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E6" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.505</v>
+        <v>0.833333</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.792079</v>
       </c>
       <c r="I6" t="n">
-        <v>0.671096</v>
+        <v>0.812183</v>
       </c>
       <c r="J6" t="n">
-        <v>0.250175</v>
+        <v>0.135272</v>
       </c>
       <c r="K6" t="n">
-        <v>0.485</v>
+        <v>0.8108109999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.773196</v>
       </c>
       <c r="M6" t="n">
-        <v>0.653199</v>
+        <v>0.791557</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_17.txt</t>
+          <t>_4_25_1_1790733931_16.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>25</v>
       </c>
       <c r="AA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1086,42 +1086,42 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.128928</v>
+        <v>0.249973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.833333</v>
+        <v>0.505</v>
       </c>
       <c r="H7" t="n">
-        <v>0.792079</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.812183</v>
+        <v>0.671096</v>
       </c>
       <c r="J7" t="n">
-        <v>0.135272</v>
+        <v>0.250174</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8108109999999999</v>
+        <v>0.485</v>
       </c>
       <c r="L7" t="n">
-        <v>0.773196</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.791557</v>
+        <v>0.653199</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,23 +1157,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_16.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_11.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>25</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1187,42 +1187,42 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.249973</v>
+        <v>0.10595</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E8" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.505</v>
+        <v>0.87659</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.852723</v>
       </c>
       <c r="I8" t="n">
-        <v>0.671096</v>
+        <v>0.864492</v>
       </c>
       <c r="J8" t="n">
-        <v>0.250175</v>
+        <v>0.101335</v>
       </c>
       <c r="K8" t="n">
-        <v>0.485</v>
+        <v>0.87766</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.850515</v>
       </c>
       <c r="M8" t="n">
-        <v>0.653199</v>
+        <v>0.863874</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,23 +1258,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_0.txt</t>
+          <t>_4_25_1_1790733931_0.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z8" t="n">
         <v>25</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1288,7 +1288,7 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.249972</v>
+        <v>0.249976</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>0.671096</v>
       </c>
       <c r="J9" t="n">
-        <v>0.250177</v>
+        <v>0.250175</v>
       </c>
       <c r="K9" t="n">
         <v>0.485</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_5.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_1.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.138441</v>
+        <v>0.197638</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.816431</v>
+        <v>0.712551</v>
       </c>
       <c r="H10" t="n">
-        <v>0.787129</v>
+        <v>0.653465</v>
       </c>
       <c r="I10" t="n">
-        <v>0.801512</v>
+        <v>0.6817299999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0.137488</v>
+        <v>0.200345</v>
       </c>
       <c r="K10" t="n">
-        <v>0.806283</v>
+        <v>0.679144</v>
       </c>
       <c r="L10" t="n">
-        <v>0.793814</v>
+        <v>0.654639</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>0.666667</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_2.txt</t>
+          <t>_4_25_1_1790733931_12.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.19603</v>
+        <v>0.249974</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.70719</v>
+        <v>0.505</v>
       </c>
       <c r="H12" t="n">
-        <v>0.669554</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.687858</v>
+        <v>0.671096</v>
       </c>
       <c r="J12" t="n">
-        <v>0.197052</v>
+        <v>0.250167</v>
       </c>
       <c r="K12" t="n">
-        <v>0.664894</v>
+        <v>0.485</v>
       </c>
       <c r="L12" t="n">
-        <v>0.64433</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.65445</v>
+        <v>0.653199</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_18.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_19.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>25</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,42 +1692,42 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.12563</v>
+        <v>0.249973</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F13" t="n">
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.819059</v>
+        <v>0.505</v>
       </c>
       <c r="H13" t="n">
-        <v>0.840347</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.829566</v>
+        <v>0.671096</v>
       </c>
       <c r="J13" t="n">
-        <v>0.12964</v>
+        <v>0.250176</v>
       </c>
       <c r="K13" t="n">
-        <v>0.785366</v>
+        <v>0.485</v>
       </c>
       <c r="L13" t="n">
-        <v>0.829897</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.807018</v>
+        <v>0.653199</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,23 +1763,23 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_7.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_15.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z13" t="n">
         <v>25</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.249975</v>
+        <v>0.249973</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_7.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_0.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1894,42 +1894,42 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.249975</v>
+        <v>0.13342</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E15" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.505</v>
+        <v>0.811966</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.82302</v>
       </c>
       <c r="I15" t="n">
-        <v>0.671096</v>
+        <v>0.817455</v>
       </c>
       <c r="J15" t="n">
-        <v>0.250175</v>
+        <v>0.138677</v>
       </c>
       <c r="K15" t="n">
-        <v>0.485</v>
+        <v>0.772277</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.8041239999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.653199</v>
+        <v>0.787879</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,23 +1965,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_6.txt</t>
+          <t>_4_25_1_1790733931_17.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>25</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.13342</v>
+        <v>0.09209199999999999</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2012,25 +2012,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.811966</v>
+        <v>0.899624</v>
       </c>
       <c r="H16" t="n">
-        <v>0.82302</v>
+        <v>0.8873760000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.817455</v>
+        <v>0.893458</v>
       </c>
       <c r="J16" t="n">
-        <v>0.138677</v>
+        <v>0.09658600000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.772277</v>
+        <v>0.871287</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8041239999999999</v>
+        <v>0.907216</v>
       </c>
       <c r="M16" t="n">
-        <v>0.787879</v>
+        <v>0.888889</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_17.txt</t>
+          <t>_4_25_1_1790733931_13.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.082273</v>
+        <v>0.147697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2113,25 +2113,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.900125</v>
+        <v>0.786064</v>
       </c>
       <c r="H17" t="n">
-        <v>0.892327</v>
+        <v>0.7957920000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.896209</v>
+        <v>0.790898</v>
       </c>
       <c r="J17" t="n">
-        <v>0.089388</v>
+        <v>0.145076</v>
       </c>
       <c r="K17" t="n">
-        <v>0.876289</v>
+        <v>0.812183</v>
       </c>
       <c r="L17" t="n">
-        <v>0.876289</v>
+        <v>0.824742</v>
       </c>
       <c r="M17" t="n">
-        <v>0.876289</v>
+        <v>0.818414</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_8.txt</t>
+          <t>_4_25_1_1790733931_15.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2197,42 +2197,42 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.147697</v>
+        <v>0.249975</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F18" t="n">
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.786064</v>
+        <v>0.505</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7957920000000001</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.790898</v>
+        <v>0.671096</v>
       </c>
       <c r="J18" t="n">
-        <v>0.145076</v>
+        <v>0.250178</v>
       </c>
       <c r="K18" t="n">
-        <v>0.812183</v>
+        <v>0.485</v>
       </c>
       <c r="L18" t="n">
-        <v>0.824742</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.818414</v>
+        <v>0.653199</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,23 +2268,23 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_15.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_8.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z18" t="n">
         <v>25</v>
       </c>
       <c r="AA18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2298,7 +2298,7 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.249978</v>
+        <v>0.249977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>0.671096</v>
       </c>
       <c r="J19" t="n">
-        <v>0.250178</v>
+        <v>0.250174</v>
       </c>
       <c r="K19" t="n">
         <v>0.485</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_2.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_13.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2399,7 +2399,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.249974</v>
+        <v>0.249978</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>0.671096</v>
       </c>
       <c r="J20" t="n">
-        <v>0.250167</v>
+        <v>0.250178</v>
       </c>
       <c r="K20" t="n">
         <v>0.485</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_19.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_2.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2500,7 +2500,7 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.10595</v>
+        <v>0.158494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2517,25 +2517,25 @@
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.87659</v>
+        <v>0.7949040000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.852723</v>
+        <v>0.772277</v>
       </c>
       <c r="I21" t="n">
-        <v>0.864492</v>
+        <v>0.783428</v>
       </c>
       <c r="J21" t="n">
-        <v>0.101335</v>
+        <v>0.163865</v>
       </c>
       <c r="K21" t="n">
-        <v>0.87766</v>
+        <v>0.797814</v>
       </c>
       <c r="L21" t="n">
-        <v>0.850515</v>
+        <v>0.7525770000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.863874</v>
+        <v>0.774536</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_0.txt</t>
+          <t>_4_25_1_1790733931_19.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2601,42 +2601,42 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.249976</v>
+        <v>0.122143</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E22" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F22" t="n">
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.505</v>
+        <v>0.825553</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0.831683</v>
       </c>
       <c r="I22" t="n">
-        <v>0.671096</v>
+        <v>0.828607</v>
       </c>
       <c r="J22" t="n">
-        <v>0.250175</v>
+        <v>0.138539</v>
       </c>
       <c r="K22" t="n">
-        <v>0.485</v>
+        <v>0.794872</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.798969</v>
       </c>
       <c r="M22" t="n">
-        <v>0.653199</v>
+        <v>0.796915</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_1.txt</t>
+          <t>_4_25_1_1790733931_11.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z22" t="n">
         <v>25</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2702,42 +2702,42 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.249975</v>
+        <v>0.12563</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E23" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F23" t="n">
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.505</v>
+        <v>0.819059</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.840347</v>
       </c>
       <c r="I23" t="n">
-        <v>0.671096</v>
+        <v>0.829566</v>
       </c>
       <c r="J23" t="n">
-        <v>0.250181</v>
+        <v>0.12964</v>
       </c>
       <c r="K23" t="n">
-        <v>0.485</v>
+        <v>0.785366</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.829897</v>
       </c>
       <c r="M23" t="n">
-        <v>0.653199</v>
+        <v>0.807018</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,23 +2773,23 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_4.txt</t>
+          <t>_4_25_1_1790733931_7.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z23" t="n">
         <v>25</v>
       </c>
       <c r="AA23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2803,42 +2803,42 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.158494</v>
+        <v>0.24997</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E24" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F24" t="n">
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7949040000000001</v>
+        <v>0.505</v>
       </c>
       <c r="H24" t="n">
-        <v>0.772277</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.783428</v>
+        <v>0.671096</v>
       </c>
       <c r="J24" t="n">
-        <v>0.163865</v>
+        <v>0.250173</v>
       </c>
       <c r="K24" t="n">
-        <v>0.797814</v>
+        <v>0.485</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7525770000000001</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0.774536</v>
+        <v>0.653199</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,23 +2874,23 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_19.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_3.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z24" t="n">
         <v>25</v>
       </c>
       <c r="AA24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -2904,42 +2904,42 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.249977</v>
+        <v>0.205443</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E25" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.505</v>
+        <v>0.698039</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.660891</v>
       </c>
       <c r="I25" t="n">
-        <v>0.671096</v>
+        <v>0.678957</v>
       </c>
       <c r="J25" t="n">
-        <v>0.250174</v>
+        <v>0.210977</v>
       </c>
       <c r="K25" t="n">
-        <v>0.485</v>
+        <v>0.654054</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.623711</v>
       </c>
       <c r="M25" t="n">
-        <v>0.653199</v>
+        <v>0.638522</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,23 +2975,23 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_13.txt</t>
+          <t>_4_25_1_1790733931_3.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z25" t="n">
         <v>25</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3005,42 +3005,42 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.122143</v>
+        <v>0.249975</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E26" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.825553</v>
+        <v>0.505</v>
       </c>
       <c r="H26" t="n">
-        <v>0.831683</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0.828607</v>
+        <v>0.671096</v>
       </c>
       <c r="J26" t="n">
-        <v>0.138539</v>
+        <v>0.250175</v>
       </c>
       <c r="K26" t="n">
-        <v>0.794872</v>
+        <v>0.485</v>
       </c>
       <c r="L26" t="n">
-        <v>0.798969</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0.796915</v>
+        <v>0.653199</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,23 +3076,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_11.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_7.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>25</v>
       </c>
       <c r="AA26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.167673</v>
+        <v>0.138441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3123,25 +3123,25 @@
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.785146</v>
+        <v>0.816431</v>
       </c>
       <c r="H27" t="n">
-        <v>0.732673</v>
+        <v>0.787129</v>
       </c>
       <c r="I27" t="n">
-        <v>0.758003</v>
+        <v>0.801512</v>
       </c>
       <c r="J27" t="n">
-        <v>0.172935</v>
+        <v>0.137488</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7627119999999999</v>
+        <v>0.806283</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6958760000000001</v>
+        <v>0.793814</v>
       </c>
       <c r="M27" t="n">
-        <v>0.727763</v>
+        <v>0.8</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_9.txt</t>
+          <t>_4_25_1_1790733931_2.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3207,42 +3207,42 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.249975</v>
+        <v>0.210265</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E28" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F28" t="n">
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.505</v>
+        <v>0.668374</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.6460399999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.671096</v>
+        <v>0.657017</v>
       </c>
       <c r="J28" t="n">
-        <v>0.250173</v>
+        <v>0.20414</v>
       </c>
       <c r="K28" t="n">
-        <v>0.485</v>
+        <v>0.687831</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0.670103</v>
       </c>
       <c r="M28" t="n">
-        <v>0.653199</v>
+        <v>0.678851</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,23 +3278,23 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_10.txt</t>
+          <t>_4_25_1_1790733931_5.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z28" t="n">
         <v>25</v>
       </c>
       <c r="AA28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3334,7 +3334,7 @@
         <v>0.671096</v>
       </c>
       <c r="J29" t="n">
-        <v>0.250177</v>
+        <v>0.250173</v>
       </c>
       <c r="K29" t="n">
         <v>0.485</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_18.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_10.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3409,42 +3409,42 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.141811</v>
+        <v>0.249977</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E30" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F30" t="n">
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.794718</v>
+        <v>0.505</v>
       </c>
       <c r="H30" t="n">
-        <v>0.819307</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.806825</v>
+        <v>0.671096</v>
       </c>
       <c r="J30" t="n">
-        <v>0.157444</v>
+        <v>0.250174</v>
       </c>
       <c r="K30" t="n">
-        <v>0.770833</v>
+        <v>0.485</v>
       </c>
       <c r="L30" t="n">
-        <v>0.762887</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0.766839</v>
+        <v>0.653199</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3480,23 +3480,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_1.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_14.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z30" t="n">
         <v>25</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3510,42 +3510,42 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.197638</v>
+        <v>0.249973</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E31" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F31" t="n">
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.712551</v>
+        <v>0.505</v>
       </c>
       <c r="H31" t="n">
-        <v>0.653465</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6817299999999999</v>
+        <v>0.671096</v>
       </c>
       <c r="J31" t="n">
-        <v>0.200345</v>
+        <v>0.250175</v>
       </c>
       <c r="K31" t="n">
-        <v>0.679144</v>
+        <v>0.485</v>
       </c>
       <c r="L31" t="n">
-        <v>0.654639</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0.666667</v>
+        <v>0.653199</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,23 +3581,23 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_12.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_9.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z31" t="n">
         <v>25</v>
       </c>
       <c r="AA31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3611,7 +3611,7 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.249973</v>
+        <v>0.249975</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>0.671096</v>
       </c>
       <c r="J32" t="n">
-        <v>0.250176</v>
+        <v>0.250175</v>
       </c>
       <c r="K32" t="n">
         <v>0.485</v>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_15.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_6.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3712,7 +3712,7 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.14035</v>
+        <v>0.167673</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3729,25 +3729,25 @@
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.793802</v>
+        <v>0.785146</v>
       </c>
       <c r="H33" t="n">
-        <v>0.824257</v>
+        <v>0.732673</v>
       </c>
       <c r="I33" t="n">
-        <v>0.808743</v>
+        <v>0.758003</v>
       </c>
       <c r="J33" t="n">
-        <v>0.151785</v>
+        <v>0.172935</v>
       </c>
       <c r="K33" t="n">
-        <v>0.747525</v>
+        <v>0.7627119999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>0.778351</v>
+        <v>0.6958760000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>0.762626</v>
+        <v>0.727763</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_6.txt</t>
+          <t>_4_25_1_1790733931_9.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3813,42 +3813,42 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.249973</v>
+        <v>0.19603</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E34" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F34" t="n">
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.505</v>
+        <v>0.70719</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0.669554</v>
       </c>
       <c r="I34" t="n">
-        <v>0.671096</v>
+        <v>0.687858</v>
       </c>
       <c r="J34" t="n">
-        <v>0.250174</v>
+        <v>0.197052</v>
       </c>
       <c r="K34" t="n">
-        <v>0.485</v>
+        <v>0.664894</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0.64433</v>
       </c>
       <c r="M34" t="n">
-        <v>0.653199</v>
+        <v>0.65445</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3884,23 +3884,23 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_11.txt</t>
+          <t>_4_25_1_1790733931_18.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z34" t="n">
         <v>25</v>
       </c>
       <c r="AA34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -3914,42 +3914,42 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.249977</v>
+        <v>0.141811</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_</t>
+          <t>_4_25_1_</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1790734006</v>
+        <v>1790733931</v>
       </c>
       <c r="E35" t="n">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F35" t="n">
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.505</v>
+        <v>0.794718</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0.819307</v>
       </c>
       <c r="I35" t="n">
-        <v>0.671096</v>
+        <v>0.806825</v>
       </c>
       <c r="J35" t="n">
-        <v>0.250174</v>
+        <v>0.157444</v>
       </c>
       <c r="K35" t="n">
-        <v>0.485</v>
+        <v>0.770833</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0.762887</v>
       </c>
       <c r="M35" t="n">
-        <v>0.653199</v>
+        <v>0.766839</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,23 +3985,23 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_14.txt</t>
+          <t>_4_25_1_1790733931_1.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 5]</t>
+          <t>[25]</t>
         </is>
       </c>
       <c r="Z35" t="n">
         <v>25</v>
       </c>
       <c r="AA35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4015,7 +4015,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.249973</v>
+        <v>0.249975</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>0.671096</v>
       </c>
       <c r="J36" t="n">
-        <v>0.250175</v>
+        <v>0.250177</v>
       </c>
       <c r="K36" t="n">
         <v>0.485</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_9.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_18.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4217,7 +4217,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.249975</v>
+        <v>0.249974</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>0.671096</v>
       </c>
       <c r="J38" t="n">
-        <v>0.250178</v>
+        <v>0.250175</v>
       </c>
       <c r="K38" t="n">
         <v>0.485</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_4_5_5_5_5_5_1_1790734006_8.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_17.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4318,42 +4318,42 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.205443</v>
+        <v>0.249972</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E39" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.698039</v>
+        <v>0.505</v>
       </c>
       <c r="H39" t="n">
-        <v>0.660891</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0.678957</v>
+        <v>0.671096</v>
       </c>
       <c r="J39" t="n">
-        <v>0.210977</v>
+        <v>0.250177</v>
       </c>
       <c r="K39" t="n">
-        <v>0.654054</v>
+        <v>0.485</v>
       </c>
       <c r="L39" t="n">
-        <v>0.623711</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>0.638522</v>
+        <v>0.653199</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_3.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_5.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>25</v>
       </c>
       <c r="AA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.210265</v>
+        <v>0.14035</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4436,25 +4436,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.668374</v>
+        <v>0.793802</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6460399999999999</v>
+        <v>0.824257</v>
       </c>
       <c r="I40" t="n">
-        <v>0.657017</v>
+        <v>0.808743</v>
       </c>
       <c r="J40" t="n">
-        <v>0.20414</v>
+        <v>0.151785</v>
       </c>
       <c r="K40" t="n">
-        <v>0.687831</v>
+        <v>0.747525</v>
       </c>
       <c r="L40" t="n">
-        <v>0.670103</v>
+        <v>0.778351</v>
       </c>
       <c r="M40" t="n">
-        <v>0.678851</v>
+        <v>0.762626</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_5.txt</t>
+          <t>_4_25_1_1790733931_6.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4520,42 +4520,42 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.09209199999999999</v>
+        <v>0.249977</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_4_25_1_</t>
+          <t>_4_5_5_5_5_5_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790733931</v>
+        <v>1790734006</v>
       </c>
       <c r="E41" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.899624</v>
+        <v>0.505</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8873760000000001</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.893458</v>
+        <v>0.671096</v>
       </c>
       <c r="J41" t="n">
-        <v>0.09658600000000001</v>
+        <v>0.250179</v>
       </c>
       <c r="K41" t="n">
-        <v>0.871287</v>
+        <v>0.485</v>
       </c>
       <c r="L41" t="n">
-        <v>0.907216</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.888889</v>
+        <v>0.653199</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,28 +4591,28 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_4_25_1_1790733931_13.txt</t>
+          <t>_4_5_5_5_5_5_1_1790734006_16.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 5, 5, 5, 5]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>25</v>
       </c>
       <c r="AA41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
     </row>
